--- a/web/files/九龙-启德-柏蔚森 I.xlsx
+++ b/web/files/九龙-启德-柏蔚森 I.xlsx
@@ -2766,7 +2766,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -19360,7 +19360,7 @@
           <t>E | 391呎 (2房)
 $866万
 $22,159/呎
-(26年-07月-31日)</t>
+(26年-09月-04日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">

--- a/web/files/九龙-启德-柏蔚森 I.xlsx
+++ b/web/files/九龙-启德-柏蔚森 I.xlsx
@@ -1136,7 +1136,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -19107,7 +19107,7 @@
           <t>C | 560呎 (3房)
 $1641万
 $29,300/呎
-(26年-08月-21日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -19423,7 +19423,7 @@
           <t>C | 560呎 (3房)
 $1405万
 $25,093/呎
-(26年-08月-13日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">

--- a/web/files/九龙-启德-柏蔚森 I.xlsx
+++ b/web/files/九龙-启德-柏蔚森 I.xlsx
@@ -3852,7 +3852,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -19526,7 +19526,7 @@
           <t>F | 400呎 (2房)
 $871万
 $21,780/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">

--- a/web/files/九龙-启德-柏蔚森 I.xlsx
+++ b/web/files/九龙-启德-柏蔚森 I.xlsx
@@ -13663,7 +13663,7 @@
         </is>
       </c>
       <c r="E209" s="4" t="n">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
         <v>9629000</v>
       </c>
       <c r="I209" s="5" t="n">
-        <v>18807</v>
+        <v>18843</v>
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         <v>9629000</v>
       </c>
       <c r="L209" s="5" t="n">
-        <v>18807</v>
+        <v>18843</v>
       </c>
       <c r="M209" s="3" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         </is>
       </c>
       <c r="E285" s="4" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F285" s="3" t="inlineStr">
         <is>
@@ -18407,7 +18407,7 @@
         <v>3864000</v>
       </c>
       <c r="I285" s="5" t="n">
-        <v>16513</v>
+        <v>16443</v>
       </c>
       <c r="J285" s="3" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>3864000</v>
       </c>
       <c r="L285" s="5" t="n">
-        <v>16513</v>
+        <v>16443</v>
       </c>
       <c r="M285" s="3" t="inlineStr">
         <is>
@@ -20826,9 +20826,9 @@
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>A | 512呎 (3房)
+          <t>A | 511呎 (3房)
 $963万
-$18,807/呎
+$18,843/呎
 (24年-08月-02日)</t>
         </is>
       </c>
@@ -21745,9 +21745,9 @@
       </c>
       <c r="J9" s="20" t="inlineStr">
         <is>
-          <t>J | 234呎 (1房)
+          <t>J | 235呎 (1房)
 $386万
-$16,513/呎
+$16,443/呎
 (24年-08月-02日)</t>
         </is>
       </c>

--- a/web/files/九龙-启德-柏蔚森 I.xlsx
+++ b/web/files/九龙-启德-柏蔚森 I.xlsx
@@ -16093,38 +16093,30 @@
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H248" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I248" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="H248" s="5" t="n">
+        <v>9434000</v>
+      </c>
+      <c r="I248" s="5" t="n">
+        <v>24504</v>
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K248" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L248" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K248" s="5" t="n">
+        <v>9434000</v>
+      </c>
+      <c r="L248" s="5" t="n">
+        <v>24504</v>
       </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
@@ -16133,7 +16125,7 @@
       </c>
       <c r="N248" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -21059,7 +21051,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -21069,7 +21061,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -21298,12 +21290,12 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 385呎 (2房)
-招标单位
--
-(在售)</t>
+$943万
+$24,504/呎
+(26年-10月-09日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">

--- a/web/files/九龙-启德-柏蔚森 I.xlsx
+++ b/web/files/九龙-启德-柏蔚森 I.xlsx
@@ -10865,7 +10865,7 @@
         </is>
       </c>
       <c r="E164" s="4" t="n">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>11057000</v>
       </c>
       <c r="I164" s="5" t="n">
-        <v>21596</v>
+        <v>21638</v>
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
@@ -10892,7 +10892,7 @@
         <v>11057000</v>
       </c>
       <c r="L164" s="5" t="n">
-        <v>21596</v>
+        <v>21638</v>
       </c>
       <c r="M164" s="3" t="inlineStr">
         <is>
@@ -20423,9 +20423,9 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>A | 512呎 (3房)
+          <t>A | 511呎 (3房)
 $1106万
-$21,596/呎
+$21,638/呎
 (26年-07月-17日)</t>
         </is>
       </c>

--- a/web/files/九龙-启德-柏蔚森 I.xlsx
+++ b/web/files/九龙-启德-柏蔚森 I.xlsx
@@ -9187,38 +9187,30 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H137" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I137" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="H137" s="5" t="n">
+        <v>11593000</v>
+      </c>
+      <c r="I137" s="5" t="n">
+        <v>22643</v>
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K137" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L137" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K137" s="5" t="n">
+        <v>11593000</v>
+      </c>
+      <c r="L137" s="5" t="n">
+        <v>22643</v>
       </c>
       <c r="M137" s="3" t="inlineStr">
         <is>
@@ -9227,7 +9219,7 @@
       </c>
       <c r="N137" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -18996,7 +18988,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -19006,7 +18998,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>199</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -20184,12 +20176,12 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
-招标单位
--
-(在售)</t>
+$1159万
+$22,643/呎
+(26年-10月-18日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">

--- a/web/files/九龙-启德-柏蔚森 I.xlsx
+++ b/web/files/九龙-启德-柏蔚森 I.xlsx
@@ -10857,7 +10857,7 @@
         </is>
       </c>
       <c r="E164" s="4" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>11057000</v>
       </c>
       <c r="I164" s="5" t="n">
-        <v>21638</v>
+        <v>21596</v>
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>11057000</v>
       </c>
       <c r="L164" s="5" t="n">
-        <v>21638</v>
+        <v>21596</v>
       </c>
       <c r="M164" s="3" t="inlineStr">
         <is>
@@ -13655,7 +13655,7 @@
         </is>
       </c>
       <c r="E209" s="4" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>9629000</v>
       </c>
       <c r="I209" s="5" t="n">
-        <v>18843</v>
+        <v>18807</v>
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>9629000</v>
       </c>
       <c r="L209" s="5" t="n">
-        <v>18843</v>
+        <v>18807</v>
       </c>
       <c r="M209" s="3" t="inlineStr">
         <is>
@@ -18375,7 +18375,7 @@
         </is>
       </c>
       <c r="E285" s="4" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F285" s="3" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         <v>3864000</v>
       </c>
       <c r="I285" s="5" t="n">
-        <v>16443</v>
+        <v>16513</v>
       </c>
       <c r="J285" s="3" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>3864000</v>
       </c>
       <c r="L285" s="5" t="n">
-        <v>16443</v>
+        <v>16513</v>
       </c>
       <c r="M285" s="3" t="inlineStr">
         <is>
@@ -20415,9 +20415,9 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>A | 511呎 (3房)
+          <t>A | 512呎 (3房)
 $1106万
-$21,638/呎
+$21,596/呎
 (26年-07月-17日)</t>
         </is>
       </c>
@@ -20810,9 +20810,9 @@
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>A | 511呎 (3房)
+          <t>A | 512呎 (3房)
 $963万
-$18,843/呎
+$18,807/呎
 (24年-08月-02日)</t>
         </is>
       </c>
@@ -21729,9 +21729,9 @@
       </c>
       <c r="J9" s="20" t="inlineStr">
         <is>
-          <t>J | 235呎 (1房)
+          <t>J | 234呎 (1房)
 $386万
-$16,443/呎
+$16,513/呎
 (24年-08月-02日)</t>
         </is>
       </c>
